--- a/Result/profitability/4104.xlsx
+++ b/Result/profitability/4104.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>1.09</v>
       </c>
       <c r="M2" t="n">
-        <v>1.15875</v>
+        <v>1.23375</v>
       </c>
       <c r="N2" t="n">
-        <v>22.2075</v>
+        <v>22.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.36</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07125</v>
+        <v>1.13125</v>
       </c>
       <c r="N3" t="n">
-        <v>23.3925</v>
+        <v>23.30625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.61</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>1.05875</v>
       </c>
       <c r="N4" t="n">
-        <v>23.55</v>
+        <v>23.61</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.86</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9587500000000001</v>
+        <v>0.99</v>
       </c>
       <c r="N5" t="n">
-        <v>23.4</v>
+        <v>23.415</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.83</v>
       </c>
       <c r="M6" t="n">
-        <v>0.88625</v>
+        <v>0.9575</v>
       </c>
       <c r="N6" t="n">
-        <v>21.82875</v>
+        <v>21.92875</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.04</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8800000000000001</v>
+        <v>0.9462499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>20.32375</v>
+        <v>20.33125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.89</v>
       </c>
       <c r="M8" t="n">
-        <v>0.85</v>
+        <v>0.9175</v>
       </c>
       <c r="N8" t="n">
-        <v>18.7975</v>
+        <v>18.845</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.89</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8212499999999999</v>
+        <v>0.82125</v>
       </c>
       <c r="N9" t="n">
         <v>17.15875</v>
@@ -1645,7 +1645,7 @@
         <v>0.87</v>
       </c>
       <c r="M10" t="n">
-        <v>0.79375</v>
+        <v>0.7937500000000001</v>
       </c>
       <c r="N10" t="n">
         <v>14.9575</v>
@@ -1772,7 +1772,7 @@
         <v>0.77</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8450000000000001</v>
+        <v>0.845</v>
       </c>
       <c r="N11" t="n">
         <v>12.375</v>
@@ -2020,7 +2020,7 @@
         <v>0.89</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9262499999999999</v>
+        <v>0.92625</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
@@ -9810,6 +9810,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2386</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1869</v>
+      </c>
+      <c r="E75" t="n">
+        <v>518</v>
+      </c>
+      <c r="F75" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="G75" t="n">
+        <v>193</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.11%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>224</v>
+      </c>
+      <c r="J75" t="n">
+        <v>418</v>
+      </c>
+      <c r="K75" t="n">
+        <v>308</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="N75" t="n">
+        <v>21.50375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.5399999999999998</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.482142857142857</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.3800000000000026</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01783200375410621</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.177304964539007</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.120000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.005563282336578546</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
